--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:50</t>
+    <t xml:space="preserve">2026-09-10 01:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:00</t>
+    <t xml:space="preserve">2026-09-18 11:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:07</t>
+    <t xml:space="preserve">2026-09-23 14:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:30</t>
+    <t xml:space="preserve">2026-10-02 15:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Florida</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Mulchén</t>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Nacimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:21</t>
+    <t xml:space="preserve">2026-10-04 10:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:16</t>
+    <t xml:space="preserve">2026-10-05 15:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
